--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128582671</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582660</v>
       </c>
       <c r="B4" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128582663</v>
       </c>
       <c r="B5" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128582670</v>
       </c>
       <c r="B6" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128582658</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,6 +1264,103 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128667135</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97460</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>787534</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7370549</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128582663</v>
+        <v>128582670</v>
       </c>
       <c r="B5" t="n">
-        <v>97454</v>
+        <v>91460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>787554</v>
+        <v>787633</v>
       </c>
       <c r="R5" t="n">
-        <v>7370493</v>
+        <v>7370460</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128582670</v>
+        <v>128582663</v>
       </c>
       <c r="B6" t="n">
-        <v>91454</v>
+        <v>97460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787633</v>
+        <v>787554</v>
       </c>
       <c r="R6" t="n">
-        <v>7370460</v>
+        <v>7370493</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1270,7 +1270,7 @@
         <v>128667135</v>
       </c>
       <c r="B8" t="n">
-        <v>97460</v>
+        <v>97466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128582670</v>
+        <v>128582663</v>
       </c>
       <c r="B5" t="n">
-        <v>91460</v>
+        <v>97460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>787633</v>
+        <v>787554</v>
       </c>
       <c r="R5" t="n">
-        <v>7370460</v>
+        <v>7370493</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128582663</v>
+        <v>128582670</v>
       </c>
       <c r="B6" t="n">
-        <v>97460</v>
+        <v>91460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787554</v>
+        <v>787633</v>
       </c>
       <c r="R6" t="n">
-        <v>7370493</v>
+        <v>7370460</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128582671</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128582663</v>
+        <v>128582670</v>
       </c>
       <c r="B5" t="n">
-        <v>97460</v>
+        <v>91462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>787554</v>
+        <v>787633</v>
       </c>
       <c r="R5" t="n">
-        <v>7370493</v>
+        <v>7370460</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128582670</v>
+        <v>128582663</v>
       </c>
       <c r="B6" t="n">
-        <v>91460</v>
+        <v>97462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787633</v>
+        <v>787554</v>
       </c>
       <c r="R6" t="n">
-        <v>7370460</v>
+        <v>7370493</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1270,7 +1270,7 @@
         <v>128667135</v>
       </c>
       <c r="B8" t="n">
-        <v>97466</v>
+        <v>97468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128582670</v>
       </c>
       <c r="B5" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128582663</v>
       </c>
       <c r="B6" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128667135</v>
       </c>
       <c r="B8" t="n">
-        <v>97468</v>
+        <v>97469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128582671</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582660</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128582670</v>
       </c>
       <c r="B5" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128582663</v>
       </c>
       <c r="B6" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128582658</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128667135</v>
       </c>
       <c r="B8" t="n">
-        <v>97469</v>
+        <v>97496</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128582671</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128582670</v>
+        <v>128582663</v>
       </c>
       <c r="B5" t="n">
-        <v>91490</v>
+        <v>97496</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>787633</v>
+        <v>787554</v>
       </c>
       <c r="R5" t="n">
-        <v>7370460</v>
+        <v>7370493</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128582663</v>
+        <v>128582670</v>
       </c>
       <c r="B6" t="n">
-        <v>97490</v>
+        <v>91495</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787554</v>
+        <v>787633</v>
       </c>
       <c r="R6" t="n">
-        <v>7370493</v>
+        <v>7370460</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1270,7 +1270,7 @@
         <v>128667135</v>
       </c>
       <c r="B8" t="n">
-        <v>97496</v>
+        <v>97502</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128582663</v>
       </c>
       <c r="B5" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128582670</v>
       </c>
       <c r="B6" t="n">
-        <v>91495</v>
+        <v>91500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128667135</v>
       </c>
       <c r="B8" t="n">
-        <v>97502</v>
+        <v>97509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128582663</v>
+        <v>128582670</v>
       </c>
       <c r="B5" t="n">
-        <v>97503</v>
+        <v>91500</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>787554</v>
+        <v>787633</v>
       </c>
       <c r="R5" t="n">
-        <v>7370493</v>
+        <v>7370460</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128582670</v>
+        <v>128582663</v>
       </c>
       <c r="B6" t="n">
-        <v>91500</v>
+        <v>97503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787633</v>
+        <v>787554</v>
       </c>
       <c r="R6" t="n">
-        <v>7370460</v>
+        <v>7370493</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128582671</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582660</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128582670</v>
       </c>
       <c r="B5" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128582663</v>
       </c>
       <c r="B6" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128582658</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128667135</v>
       </c>
       <c r="B8" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128582671</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582660</v>
       </c>
       <c r="B4" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128582670</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128582663</v>
       </c>
       <c r="B6" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128582658</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128667135</v>
       </c>
       <c r="B8" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128582671</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128582670</v>
+        <v>128582663</v>
       </c>
       <c r="B5" t="n">
-        <v>91511</v>
+        <v>97522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>787633</v>
+        <v>787554</v>
       </c>
       <c r="R5" t="n">
-        <v>7370460</v>
+        <v>7370493</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128582663</v>
+        <v>128582670</v>
       </c>
       <c r="B6" t="n">
-        <v>97517</v>
+        <v>91516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787554</v>
+        <v>787633</v>
       </c>
       <c r="R6" t="n">
-        <v>7370493</v>
+        <v>7370460</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1270,7 +1270,7 @@
         <v>128667135</v>
       </c>
       <c r="B8" t="n">
-        <v>97523</v>
+        <v>97528</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128582671</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128582663</v>
       </c>
       <c r="B5" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128582670</v>
       </c>
       <c r="B6" t="n">
-        <v>91516</v>
+        <v>91522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>128667135</v>
       </c>
       <c r="B8" t="n">
-        <v>97528</v>
+        <v>97536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128582663</v>
+        <v>128582670</v>
       </c>
       <c r="B5" t="n">
-        <v>97530</v>
+        <v>91522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>787554</v>
+        <v>787633</v>
       </c>
       <c r="R5" t="n">
-        <v>7370493</v>
+        <v>7370460</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128582670</v>
+        <v>128582663</v>
       </c>
       <c r="B6" t="n">
-        <v>91522</v>
+        <v>97530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787633</v>
+        <v>787554</v>
       </c>
       <c r="R6" t="n">
-        <v>7370460</v>
+        <v>7370493</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 39504-2025 artfynd.xlsx
+++ b/artfynd/A 39504-2025 artfynd.xlsx
@@ -1270,7 +1270,7 @@
         <v>128667135</v>
       </c>
       <c r="B8" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
